--- a/cache/sandogh.xlsx
+++ b/cache/sandogh.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\شفیع زاده\فرم ها\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE81A92-C489-45B6-980D-7814E85F2607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E261CB-6872-4FA6-BB33-6766FA0A4516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C07556EF-07C2-4F55-A550-BB27D149BF14}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" firstSheet="2" activeTab="2" xr2:uid="{C07556EF-07C2-4F55-A550-BB27D149BF14}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -217,8 +217,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_-_ ;_ * #,##0.00\-_ ;_ * &quot;-&quot;??_-_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_-_ ;_ * #,##0\-_ ;_ * &quot;-&quot;??_-_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_-_ ;_ * #,##0.00\-_ ;_ * &quot;-&quot;??_-_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_-_ ;_ * #,##0\-_ ;_ * &quot;-&quot;??_-_ ;_ @_ "/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -482,9 +482,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -591,16 +591,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -610,51 +608,66 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -685,39 +698,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -875,9 +855,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -915,7 +895,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1021,7 +1001,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1163,7 +1143,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1398,16 +1378,16 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="2:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="76"/>
+      <c r="C14" s="75"/>
       <c r="D14" s="21"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="80"/>
+      <c r="G14" s="79"/>
       <c r="H14" s="22"/>
     </row>
     <row r="15" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.6">
@@ -1429,17 +1409,17 @@
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="2:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B17" s="77" t="s">
+      <c r="B17" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="77"/>
-      <c r="D17" s="78"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="77"/>
       <c r="E17" s="26"/>
-      <c r="F17" s="79" t="s">
+      <c r="F17" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
     </row>
     <row r="18" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="27" t="s">
@@ -1691,10 +1671,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="82"/>
+      <c r="C2" s="81"/>
       <c r="D2" s="34" t="s">
         <v>3</v>
       </c>
@@ -1810,23 +1790,23 @@
       <c r="D12" s="33"/>
     </row>
     <row r="13" spans="2:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="84"/>
+      <c r="C13" s="83"/>
       <c r="D13" s="45"/>
     </row>
     <row r="14" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.65"/>
     <row r="15" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.65"/>
     <row r="16" spans="2:7" x14ac:dyDescent="0.65">
-      <c r="C16" s="77" t="s">
+      <c r="C16" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="77"/>
-      <c r="F16" s="78" t="s">
+      <c r="D16" s="76"/>
+      <c r="F16" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="79"/>
+      <c r="G16" s="78"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.65">
       <c r="B17" s="23"/>
@@ -1976,22 +1956,21 @@
     <col min="2" max="3" width="36.7109375" style="32" customWidth="1"/>
     <col min="4" max="4" width="4.28515625" style="32" customWidth="1"/>
     <col min="5" max="6" width="36.7109375" style="32" customWidth="1"/>
-    <col min="7" max="7" width="20.5703125" style="60" customWidth="1"/>
-    <col min="8" max="14" width="20.5703125" style="32" customWidth="1"/>
+    <col min="7" max="14" width="20.5703125" style="32" customWidth="1"/>
     <col min="15" max="16384" width="9" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.65"/>
     <row r="2" spans="2:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="87" t="s">
+      <c r="C2" s="73"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="88"/>
+      <c r="F2" s="70"/>
       <c r="G2" s="44" t="s">
         <v>39</v>
       </c>
@@ -2001,284 +1980,283 @@
       <c r="I2" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="66" t="s">
+      <c r="J2" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="66" t="s">
+      <c r="K2" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="66" t="s">
+      <c r="L2" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="66" t="s">
+      <c r="M2" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="66" t="s">
+      <c r="N2" s="55" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="64"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
     </row>
     <row r="4" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="48"/>
+      <c r="C4" s="63"/>
       <c r="D4" s="25"/>
       <c r="E4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="49"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
     </row>
     <row r="5" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="17"/>
+      <c r="C5" s="63"/>
       <c r="D5" s="25"/>
       <c r="E5" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="49"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
     </row>
     <row r="6" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="17"/>
+      <c r="C6" s="63"/>
       <c r="D6" s="25"/>
       <c r="E6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="49"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="33"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
     </row>
     <row r="7" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="17"/>
+      <c r="C7" s="63"/>
       <c r="D7" s="25"/>
       <c r="E7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
     </row>
     <row r="8" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B8" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="63"/>
       <c r="D8" s="25"/>
-      <c r="E8" s="54" t="s">
+      <c r="E8" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="51"/>
-      <c r="G8" s="72" t="s">
+      <c r="F8" s="64"/>
+      <c r="G8" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
     </row>
     <row r="9" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="17"/>
+      <c r="C9" s="63"/>
       <c r="D9" s="25"/>
       <c r="E9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="85" t="s">
+      <c r="F9" s="64"/>
+      <c r="G9" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="85" t="s">
+      <c r="H9" s="68"/>
+      <c r="I9" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="86"/>
-      <c r="K9" s="85" t="s">
+      <c r="J9" s="68"/>
+      <c r="K9" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="86"/>
-      <c r="M9" s="85" t="s">
+      <c r="L9" s="68"/>
+      <c r="M9" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="N9" s="86"/>
+      <c r="N9" s="68"/>
     </row>
     <row r="10" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B10" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="17"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="25"/>
       <c r="E10" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="56"/>
-      <c r="G10" s="69" t="s">
+      <c r="F10" s="64"/>
+      <c r="G10" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="H10" s="61" t="s">
+      <c r="H10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="69" t="s">
+      <c r="I10" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="J10" s="61" t="s">
+      <c r="J10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="69" t="s">
+      <c r="K10" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="L10" s="61" t="s">
+      <c r="L10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="69" t="s">
+      <c r="M10" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="N10" s="61" t="s">
+      <c r="N10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="O10" s="63"/>
+      <c r="O10" s="54"/>
     </row>
     <row r="11" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B11" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="17"/>
+      <c r="C11" s="63"/>
       <c r="D11" s="25"/>
-      <c r="E11" s="91" t="s">
+      <c r="E11" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="92"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="66"/>
     </row>
     <row r="12" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B12" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="17"/>
+      <c r="C12" s="63"/>
       <c r="D12" s="25"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="68"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="66"/>
     </row>
     <row r="13" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="51"/>
+      <c r="C13" s="63"/>
       <c r="D13" s="25"/>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="57"/>
+      <c r="F13" s="53"/>
       <c r="G13" s="65"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="68"/>
-      <c r="N13" s="68"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="66"/>
     </row>
     <row r="14" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="66"/>
     </row>
     <row r="15" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.65"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="E11:F12"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="G9:H9"/>

--- a/cache/sandogh.xlsx
+++ b/cache/sandogh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E261CB-6872-4FA6-BB33-6766FA0A4516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A98410-9BE4-4C4B-841E-A4BF0714E7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" firstSheet="2" activeTab="2" xr2:uid="{C07556EF-07C2-4F55-A550-BB27D149BF14}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{C07556EF-07C2-4F55-A550-BB27D149BF14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -654,12 +654,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -698,6 +692,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1378,16 +1378,16 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="2:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="75"/>
+      <c r="C14" s="73"/>
       <c r="D14" s="21"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="79"/>
+      <c r="G14" s="77"/>
       <c r="H14" s="22"/>
     </row>
     <row r="15" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.6">
@@ -1409,17 +1409,17 @@
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="2:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B17" s="76" t="s">
+      <c r="B17" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="76"/>
-      <c r="D17" s="77"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="75"/>
       <c r="E17" s="26"/>
-      <c r="F17" s="78" t="s">
+      <c r="F17" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="76"/>
-      <c r="H17" s="76"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
     </row>
     <row r="18" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="27" t="s">
@@ -1671,10 +1671,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="81"/>
+      <c r="C2" s="79"/>
       <c r="D2" s="34" t="s">
         <v>3</v>
       </c>
@@ -1790,23 +1790,23 @@
       <c r="D12" s="33"/>
     </row>
     <row r="13" spans="2:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="B13" s="82" t="s">
+      <c r="B13" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="83"/>
+      <c r="C13" s="81"/>
       <c r="D13" s="45"/>
     </row>
     <row r="14" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.65"/>
     <row r="15" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.65"/>
     <row r="16" spans="2:7" x14ac:dyDescent="0.65">
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="F16" s="77" t="s">
+      <c r="D16" s="74"/>
+      <c r="F16" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="78"/>
+      <c r="G16" s="76"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.65">
       <c r="B17" s="23"/>
@@ -1962,15 +1962,15 @@
   <sheetData>
     <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.65"/>
     <row r="2" spans="2:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="73"/>
+      <c r="C2" s="71"/>
       <c r="D2" s="49"/>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="70"/>
+      <c r="F2" s="83"/>
       <c r="G2" s="44" t="s">
         <v>39</v>
       </c>
@@ -2234,13 +2234,13 @@
       <c r="N13" s="66"/>
     </row>
     <row r="14" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
       <c r="G14" s="65"/>
       <c r="H14" s="66"/>
       <c r="I14" s="65"/>
@@ -2252,10 +2252,9 @@
     </row>
     <row r="15" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.65"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="E2:F2"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="K9:L9"/>
